--- a/output/laminas_comunales/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>2463703.75</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>2218923.75</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>2071883.62</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>2031121.12</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>1834589</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>1821095.62</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>1498330.12</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>1455922.12</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>1351617</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>1217796.75</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>1176513.12</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>1161805.25</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>1155403.25</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>1136902.5</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>1116308</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>1113009.5</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>1104940.25</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>1104285.5</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>1091749.38</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>1078221.88</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>1071370.88</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>1049512.62</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>1049025.62</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>1030931.69</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>1025814.38</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>1011274.81</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>1009188.06</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>994328.3100000001</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>984797.75</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>966184.88</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>962168.12</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>932971.9399999999</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -812,9 +711,6 @@
       <c r="B34">
         <v>912681.6899999999</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -825,9 +721,6 @@
       <c r="B35">
         <v>893681.75</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -838,9 +731,6 @@
       <c r="B36">
         <v>890959.5600000001</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -851,9 +741,6 @@
       <c r="B37">
         <v>884786.38</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -864,9 +751,6 @@
       <c r="B38">
         <v>881690.3100000001</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -877,9 +761,6 @@
       <c r="B39">
         <v>880655.1899999999</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,9 +771,6 @@
       <c r="B40">
         <v>865162</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -903,9 +781,6 @@
       <c r="B41">
         <v>859853.6899999999</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -916,9 +791,6 @@
       <c r="B42">
         <v>854101.75</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -929,9 +801,6 @@
       <c r="B43">
         <v>854069.9399999999</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -942,9 +811,6 @@
       <c r="B44">
         <v>852342.6899999999</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -955,9 +821,6 @@
       <c r="B45">
         <v>844964</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -968,9 +831,6 @@
       <c r="B46">
         <v>844203.0600000001</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -981,9 +841,6 @@
       <c r="B47">
         <v>823617.1899999999</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -994,9 +851,6 @@
       <c r="B48">
         <v>815337.4399999999</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1007,9 +861,6 @@
       <c r="B49">
         <v>808810.88</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1020,9 +871,6 @@
       <c r="B50">
         <v>783528.1899999999</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1033,9 +881,6 @@
       <c r="B51">
         <v>760935.75</v>
       </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1046,9 +891,6 @@
       <c r="B52">
         <v>759288.9399999999</v>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1058,9 +900,6 @@
       </c>
       <c r="B53">
         <v>716163</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>2463703.75</v>
       </c>
+      <c r="C2">
+        <v>2239329.25</v>
+      </c>
+      <c r="D2">
+        <v>224374.5</v>
+      </c>
+      <c r="E2">
+        <v>10.01971907436121</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>2218923.75</v>
       </c>
+      <c r="C3">
+        <v>2028697.62</v>
+      </c>
+      <c r="D3">
+        <v>190226.1299999999</v>
+      </c>
+      <c r="E3">
+        <v>9.376761136043532</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>2071883.62</v>
       </c>
+      <c r="C4">
+        <v>1903789.12</v>
+      </c>
+      <c r="D4">
+        <v>168094.5</v>
+      </c>
+      <c r="E4">
+        <v>8.829470566571995</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>2031121.12</v>
       </c>
+      <c r="C5">
+        <v>1816561.12</v>
+      </c>
+      <c r="D5">
+        <v>214560</v>
+      </c>
+      <c r="E5">
+        <v>11.81132842918051</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>1834589</v>
       </c>
+      <c r="C6">
+        <v>1658087</v>
+      </c>
+      <c r="D6">
+        <v>176502</v>
+      </c>
+      <c r="E6">
+        <v>10.64491790840891</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>1821095.62</v>
       </c>
+      <c r="C7">
+        <v>1651200.88</v>
+      </c>
+      <c r="D7">
+        <v>169894.7400000002</v>
+      </c>
+      <c r="E7">
+        <v>10.28916239434177</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>1498330.12</v>
       </c>
+      <c r="C8">
+        <v>1331163</v>
+      </c>
+      <c r="D8">
+        <v>167167.1200000001</v>
+      </c>
+      <c r="E8">
+        <v>12.55797524420377</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>1455922.12</v>
       </c>
+      <c r="C9">
+        <v>1325484</v>
+      </c>
+      <c r="D9">
+        <v>130438.1200000001</v>
+      </c>
+      <c r="E9">
+        <v>9.84079174097916</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>1351617</v>
       </c>
+      <c r="C10">
+        <v>1209708.88</v>
+      </c>
+      <c r="D10">
+        <v>141908.1200000001</v>
+      </c>
+      <c r="E10">
+        <v>11.73076616582332</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>1217796.75</v>
       </c>
+      <c r="C11">
+        <v>1089132.5</v>
+      </c>
+      <c r="D11">
+        <v>128664.25</v>
+      </c>
+      <c r="E11">
+        <v>11.81346163116057</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,415 +581,803 @@
       <c r="B12">
         <v>1176513.12</v>
       </c>
+      <c r="C12">
+        <v>1058416.12</v>
+      </c>
+      <c r="D12">
+        <v>118097</v>
+      </c>
+      <c r="E12">
+        <v>11.15789884228142</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B13">
-        <v>1161805.25</v>
+        <v>1173733.38</v>
+      </c>
+      <c r="C13">
+        <v>1043639.5</v>
+      </c>
+      <c r="D13">
+        <v>130093.8799999999</v>
+      </c>
+      <c r="E13">
+        <v>12.46540400205243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="B14">
-        <v>1155403.25</v>
+        <v>1161805.25</v>
+      </c>
+      <c r="C14">
+        <v>1049338</v>
+      </c>
+      <c r="D14">
+        <v>112467.25</v>
+      </c>
+      <c r="E14">
+        <v>10.71792406259946</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lampa</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="B15">
-        <v>1136902.5</v>
+        <v>1155403.25</v>
+      </c>
+      <c r="C15">
+        <v>983180.1899999999</v>
+      </c>
+      <c r="D15">
+        <v>172223.0600000001</v>
+      </c>
+      <c r="E15">
+        <v>17.51693756156742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tiltil</t>
+          <t>Lampa</t>
         </is>
       </c>
       <c r="B16">
-        <v>1116308</v>
+        <v>1136902.5</v>
+      </c>
+      <c r="C16">
+        <v>1019242.5</v>
+      </c>
+      <c r="D16">
+        <v>117660</v>
+      </c>
+      <c r="E16">
+        <v>11.54386713662352</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>Tiltil</t>
         </is>
       </c>
       <c r="B17">
-        <v>1113009.5</v>
+        <v>1116308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="B18">
-        <v>1104940.25</v>
+        <v>1113009.5</v>
+      </c>
+      <c r="C18">
+        <v>976763.4399999999</v>
+      </c>
+      <c r="D18">
+        <v>136246.0600000001</v>
+      </c>
+      <c r="E18">
+        <v>13.94872641834344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="B19">
-        <v>1104285.5</v>
+        <v>1104940.25</v>
+      </c>
+      <c r="C19">
+        <v>963317.12</v>
+      </c>
+      <c r="D19">
+        <v>141623.13</v>
+      </c>
+      <c r="E19">
+        <v>14.70161041049494</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="B20">
-        <v>1091749.38</v>
+        <v>1104285.5</v>
+      </c>
+      <c r="C20">
+        <v>1014115.31</v>
+      </c>
+      <c r="D20">
+        <v>90170.18999999994</v>
+      </c>
+      <c r="E20">
+        <v>8.891512544071546</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="B21">
-        <v>1078221.88</v>
+        <v>1091749.38</v>
+      </c>
+      <c r="C21">
+        <v>986148.12</v>
+      </c>
+      <c r="D21">
+        <v>105601.2599999999</v>
+      </c>
+      <c r="E21">
+        <v>10.70845827906663</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="B22">
-        <v>1071370.88</v>
+        <v>1078221.88</v>
+      </c>
+      <c r="C22">
+        <v>962543.88</v>
+      </c>
+      <c r="D22">
+        <v>115677.9999999999</v>
+      </c>
+      <c r="E22">
+        <v>12.01794561303531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="B23">
-        <v>1049512.62</v>
+        <v>1071370.88</v>
+      </c>
+      <c r="C23">
+        <v>946984.1899999999</v>
+      </c>
+      <c r="D23">
+        <v>124386.6899999999</v>
+      </c>
+      <c r="E23">
+        <v>13.13503343704186</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="B24">
-        <v>1049025.62</v>
+        <v>1049512.62</v>
+      </c>
+      <c r="C24">
+        <v>941701.38</v>
+      </c>
+      <c r="D24">
+        <v>107811.2400000001</v>
+      </c>
+      <c r="E24">
+        <v>11.4485592024937</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="B25">
-        <v>1030931.69</v>
+        <v>1049025.62</v>
+      </c>
+      <c r="C25">
+        <v>888140.6899999999</v>
+      </c>
+      <c r="D25">
+        <v>160884.9300000002</v>
+      </c>
+      <c r="E25">
+        <v>18.11480228430928</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="B26">
-        <v>1025814.38</v>
+        <v>1030931.69</v>
+      </c>
+      <c r="C26">
+        <v>914343.6899999999</v>
+      </c>
+      <c r="D26">
+        <v>116588</v>
+      </c>
+      <c r="E26">
+        <v>12.75100394688566</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="B27">
-        <v>1011274.81</v>
+        <v>1025814.38</v>
+      </c>
+      <c r="C27">
+        <v>915416.38</v>
+      </c>
+      <c r="D27">
+        <v>110398</v>
+      </c>
+      <c r="E27">
+        <v>12.0598672267586</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="B28">
-        <v>1009188.06</v>
+        <v>1011274.81</v>
+      </c>
+      <c r="C28">
+        <v>906517.75</v>
+      </c>
+      <c r="D28">
+        <v>104757.0600000001</v>
+      </c>
+      <c r="E28">
+        <v>11.55598552813777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="B29">
-        <v>994328.3100000001</v>
+        <v>1009188.06</v>
+      </c>
+      <c r="C29">
+        <v>911571</v>
+      </c>
+      <c r="D29">
+        <v>97617.06000000006</v>
+      </c>
+      <c r="E29">
+        <v>10.70866229838379</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="B30">
-        <v>984797.75</v>
+        <v>994328.3100000001</v>
+      </c>
+      <c r="C30">
+        <v>896728.8100000001</v>
+      </c>
+      <c r="D30">
+        <v>97599.5</v>
+      </c>
+      <c r="E30">
+        <v>10.88394829201484</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="B31">
-        <v>966184.88</v>
+        <v>984797.75</v>
+      </c>
+      <c r="C31">
+        <v>853407.5600000001</v>
+      </c>
+      <c r="D31">
+        <v>131390.1899999999</v>
+      </c>
+      <c r="E31">
+        <v>15.39594868365122</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="B32">
-        <v>962168.12</v>
+        <v>966184.88</v>
+      </c>
+      <c r="C32">
+        <v>861405.9399999999</v>
+      </c>
+      <c r="D32">
+        <v>104778.9400000001</v>
+      </c>
+      <c r="E32">
+        <v>12.16371226787687</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="B33">
-        <v>932971.9399999999</v>
+        <v>962168.12</v>
+      </c>
+      <c r="C33">
+        <v>848886.88</v>
+      </c>
+      <c r="D33">
+        <v>113281.24</v>
+      </c>
+      <c r="E33">
+        <v>13.34468027118054</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="B34">
-        <v>912681.6899999999</v>
+        <v>932971.9399999999</v>
+      </c>
+      <c r="C34">
+        <v>836037.5</v>
+      </c>
+      <c r="D34">
+        <v>96934.43999999994</v>
+      </c>
+      <c r="E34">
+        <v>11.59450861952962</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="B35">
-        <v>893681.75</v>
+        <v>912681.6899999999</v>
+      </c>
+      <c r="C35">
+        <v>815359.3100000001</v>
+      </c>
+      <c r="D35">
+        <v>97322.37999999989</v>
+      </c>
+      <c r="E35">
+        <v>11.93613402169895</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="B36">
-        <v>890959.5600000001</v>
+        <v>893681.75</v>
+      </c>
+      <c r="C36">
+        <v>796662.12</v>
+      </c>
+      <c r="D36">
+        <v>97019.63</v>
+      </c>
+      <c r="E36">
+        <v>12.17826573704797</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="B37">
-        <v>884786.38</v>
+        <v>890959.5600000001</v>
+      </c>
+      <c r="C37">
+        <v>786743.5</v>
+      </c>
+      <c r="D37">
+        <v>104216.0600000001</v>
+      </c>
+      <c r="E37">
+        <v>13.24651045734728</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="B38">
-        <v>881690.3100000001</v>
+        <v>884786.38</v>
+      </c>
+      <c r="C38">
+        <v>769117.38</v>
+      </c>
+      <c r="D38">
+        <v>115669</v>
+      </c>
+      <c r="E38">
+        <v>15.03918686637922</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="B39">
-        <v>880655.1899999999</v>
+        <v>881690.3100000001</v>
+      </c>
+      <c r="C39">
+        <v>780371.5600000001</v>
+      </c>
+      <c r="D39">
+        <v>101318.75</v>
+      </c>
+      <c r="E39">
+        <v>12.98339857490449</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>San Pedro</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="B40">
-        <v>865162</v>
+        <v>880655.1899999999</v>
+      </c>
+      <c r="C40">
+        <v>769258.3100000001</v>
+      </c>
+      <c r="D40">
+        <v>111396.8799999999</v>
+      </c>
+      <c r="E40">
+        <v>14.48107593403831</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>San Pedro</t>
         </is>
       </c>
       <c r="B41">
-        <v>859853.6899999999</v>
+        <v>865162</v>
+      </c>
+      <c r="C41">
+        <v>733994.25</v>
+      </c>
+      <c r="D41">
+        <v>131167.75</v>
+      </c>
+      <c r="E41">
+        <v>17.87040566053481</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="B42">
-        <v>854101.75</v>
+        <v>859853.6899999999</v>
+      </c>
+      <c r="C42">
+        <v>755222.6899999999</v>
+      </c>
+      <c r="D42">
+        <v>104631</v>
+      </c>
+      <c r="E42">
+        <v>13.85432421263719</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="B43">
-        <v>854069.9399999999</v>
+        <v>854101.75</v>
+      </c>
+      <c r="C43">
+        <v>751354.3100000001</v>
+      </c>
+      <c r="D43">
+        <v>102747.4399999999</v>
+      </c>
+      <c r="E43">
+        <v>13.6749651439412</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="B44">
-        <v>852342.6899999999</v>
+        <v>854069.9399999999</v>
+      </c>
+      <c r="C44">
+        <v>752523.5600000001</v>
+      </c>
+      <c r="D44">
+        <v>101546.3799999999</v>
+      </c>
+      <c r="E44">
+        <v>13.49411306139039</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="B45">
-        <v>844964</v>
+        <v>852342.6899999999</v>
+      </c>
+      <c r="C45">
+        <v>755144</v>
+      </c>
+      <c r="D45">
+        <v>97198.68999999994</v>
+      </c>
+      <c r="E45">
+        <v>12.87154370557138</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="B46">
-        <v>844203.0600000001</v>
+        <v>844964</v>
+      </c>
+      <c r="C46">
+        <v>753228.5</v>
+      </c>
+      <c r="D46">
+        <v>91735.5</v>
+      </c>
+      <c r="E46">
+        <v>12.17897357840283</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="B47">
-        <v>823617.1899999999</v>
+        <v>844203.0600000001</v>
+      </c>
+      <c r="C47">
+        <v>750653.1899999999</v>
+      </c>
+      <c r="D47">
+        <v>93549.87000000011</v>
+      </c>
+      <c r="E47">
+        <v>12.46246219242739</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="B48">
-        <v>815337.4399999999</v>
+        <v>823617.1899999999</v>
+      </c>
+      <c r="C48">
+        <v>733542.6899999999</v>
+      </c>
+      <c r="D48">
+        <v>90074.5</v>
+      </c>
+      <c r="E48">
+        <v>12.27938076787325</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="B49">
-        <v>808810.88</v>
+        <v>815337.4399999999</v>
+      </c>
+      <c r="C49">
+        <v>726585.3100000001</v>
+      </c>
+      <c r="D49">
+        <v>88752.12999999989</v>
+      </c>
+      <c r="E49">
+        <v>12.21496344317776</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="B50">
-        <v>783528.1899999999</v>
+        <v>808810.88</v>
+      </c>
+      <c r="C50">
+        <v>720350.5600000001</v>
+      </c>
+      <c r="D50">
+        <v>88460.31999999995</v>
+      </c>
+      <c r="E50">
+        <v>12.28017647407673</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="B51">
-        <v>760935.75</v>
+        <v>783528.1899999999</v>
+      </c>
+      <c r="C51">
+        <v>697353.1899999999</v>
+      </c>
+      <c r="D51">
+        <v>86175</v>
+      </c>
+      <c r="E51">
+        <v>12.35743970713033</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="B52">
-        <v>759288.9399999999</v>
+        <v>760935.75</v>
+      </c>
+      <c r="C52">
+        <v>665930.8100000001</v>
+      </c>
+      <c r="D52">
+        <v>95004.93999999994</v>
+      </c>
+      <c r="E52">
+        <v>14.26648813560676</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Lo Espejo</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>759288.9399999999</v>
+      </c>
+      <c r="C53">
+        <v>670904.8100000001</v>
+      </c>
+      <c r="D53">
+        <v>88384.12999999989</v>
+      </c>
+      <c r="E53">
+        <v>13.17387037365254</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>La Pintana</t>
         </is>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>716163</v>
+      </c>
+      <c r="C54">
+        <v>635176.5</v>
+      </c>
+      <c r="D54">
+        <v>80986.5</v>
+      </c>
+      <c r="E54">
+        <v>12.75023556444548</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -1387,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1396,530 +1396,369 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alhué</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1049025.62</v>
+          <t>San Joaquín</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1078221.88</v>
+          <t>San Miguel</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1113009.5</v>
+          <t>San Ramón</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>966184.88</v>
+          <t>Independencia</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>760935.75</v>
+          <t>La Cisterna</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>1498330.12</v>
+          <t>Peñalolén</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conchalí</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>852342.6899999999</v>
+          <t>Providencia</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Curacaví</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>984797.75</v>
+          <t>La Reina</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>823617.1899999999</v>
+          <t>Calera de Tango</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Monte</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>854101.75</v>
+          <t>Colina</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estación Central</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>890959.5600000001</v>
+          <t>Santiago</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>1455922.12</v>
+          <t>Lampa</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>880655.1899999999</v>
+          <t>Pirque</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>962168.12</v>
+          <t>Puente Alto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>1025814.38</v>
+          <t>Huechuraba</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>1161805.25</v>
+          <t>San Bernardo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Granja</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>808810.88</v>
+          <t>Curacaví</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>716163</v>
+          <t>María Pinto</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>La Reina</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>1834589</v>
+          <t>Cerrillos</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>1136902.5</v>
+          <t>Cerro Navia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>2218923.75</v>
+          <t>Vitacura</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>2031121.12</v>
+          <t>Conchalí</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>759288.9399999999</v>
+          <t>El Bosque</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>815337.4399999999</v>
+          <t>Estación Central</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Macul</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>1217796.75</v>
+          <t>La Florida</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maipú</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>1091749.38</v>
+          <t>La Granja</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>María Pinto</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>884786.38</v>
+          <t>La Pintana</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Melipilla</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>854069.9399999999</v>
+          <t>Las Condes</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>1821095.62</v>
+          <t>Lo Barnechea</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>1071370.88</v>
+          <t>Lo Espejo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paine</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>859853.6899999999</v>
+          <t>Lo Prado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>844203.0600000001</v>
+          <t>Macul</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>1049512.62</v>
+          <t>Maipú</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>1176513.12</v>
+          <t>Ñuñoa</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pirque</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>1104285.5</v>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>2071883.62</v>
+          <t>Pudahuel</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>994328.3100000001</v>
+          <t>Quilicura</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>1009188.06</v>
+          <t>Quinta Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>1011274.81</v>
+          <t>Recoleta</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>893681.75</v>
+          <t>Renca</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>881690.3100000001</v>
+          <t>El Monte</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Renca</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>844964</v>
+          <t>Padre Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>932971.9399999999</v>
+          <t>Peñaflor</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>912681.6899999999</v>
+          <t>Talagante</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>1104940.25</v>
+          <t>Paine</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>1351617</v>
+          <t>Isla de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>San Pedro</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>865162</v>
+          <t>Buin</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>783528.1899999999</v>
+          <t>San José de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>1155403.25</v>
+          <t>Tiltil</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>1030931.69</v>
+          <t>Melipilla</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tiltil</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>1116308</v>
+          <t>San Pedro</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>2463703.75</v>
+          <t>Alhué</t>
+        </is>
       </c>
     </row>
   </sheetData>
